--- a/file/result/analise.xlsx
+++ b/file/result/analise.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/67048d52181fbb0f/Documents/Projetos/classifier-cellular-automata/file/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="8_{E24FDC10-DE87-48D1-8D82-DAA411C9A97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4858A0B6-B8ED-4BB2-882B-1EB68C860278}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{E24FDC10-DE87-48D1-8D82-DAA411C9A97C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C857CE88-1C6E-4CF0-9954-1FAD432F0A8C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{71F980F3-8033-423D-A8A5-3E639018C1A0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{71F980F3-8033-423D-A8A5-3E639018C1A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,13 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -116,6 +123,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -171,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -184,7 +192,6 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -500,7 +507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13757E43-6A0D-40E9-BDDF-F678868E9770}">
-  <dimension ref="A1:Z105"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="8" max="8" width="11" customWidth="1"/>
@@ -3792,7 +3799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>3</v>
       </c>
@@ -3848,7 +3855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>4</v>
       </c>
@@ -3904,7 +3911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>5</v>
       </c>
@@ -3960,7 +3967,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>6</v>
       </c>
@@ -4016,7 +4023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>7</v>
       </c>
@@ -4072,7 +4079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>8</v>
       </c>
@@ -4128,7 +4135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>9</v>
       </c>
@@ -4184,7 +4191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>10</v>
       </c>
@@ -4239,14 +4246,8 @@
       <c r="R72" t="s">
         <v>18</v>
       </c>
-      <c r="T72" s="8"/>
-      <c r="U72" s="8"/>
-      <c r="V72" s="8"/>
-      <c r="W72" s="8"/>
-      <c r="X72" s="8"/>
-      <c r="Y72" s="8"/>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>11</v>
       </c>
@@ -4301,14 +4302,8 @@
       <c r="R73" t="s">
         <v>18</v>
       </c>
-      <c r="T73" s="8"/>
-      <c r="U73" s="8"/>
-      <c r="V73" s="8"/>
-      <c r="W73" s="8"/>
-      <c r="X73" s="8"/>
-      <c r="Y73" s="8"/>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>12</v>
       </c>
@@ -4363,14 +4358,8 @@
       <c r="R74" t="s">
         <v>18</v>
       </c>
-      <c r="T74" s="8"/>
-      <c r="U74" s="8"/>
-      <c r="V74" s="8"/>
-      <c r="W74" s="8"/>
-      <c r="X74" s="8"/>
-      <c r="Y74" s="8"/>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>13</v>
       </c>
@@ -4425,14 +4414,8 @@
       <c r="R75" t="s">
         <v>18</v>
       </c>
-      <c r="T75" s="8"/>
-      <c r="U75" s="8"/>
-      <c r="V75" s="8"/>
-      <c r="W75" s="8"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="8"/>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>14</v>
       </c>
@@ -4487,14 +4470,8 @@
       <c r="R76" t="s">
         <v>18</v>
       </c>
-      <c r="T76" s="8"/>
-      <c r="U76" s="8"/>
-      <c r="V76" s="8"/>
-      <c r="W76" s="8"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="8"/>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>15</v>
       </c>
@@ -4549,14 +4526,8 @@
       <c r="R77" t="s">
         <v>18</v>
       </c>
-      <c r="T77" s="8"/>
-      <c r="U77" s="8"/>
-      <c r="V77" s="8"/>
-      <c r="W77" s="8"/>
-      <c r="X77" s="8"/>
-      <c r="Y77" s="8"/>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>16</v>
       </c>
@@ -4612,7 +4583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>17</v>
       </c>
@@ -4667,15 +4638,8 @@
       <c r="R79" t="s">
         <v>18</v>
       </c>
-      <c r="T79" s="8"/>
-      <c r="U79" s="8"/>
-      <c r="V79" s="8"/>
-      <c r="W79" s="8"/>
-      <c r="X79" s="8"/>
-      <c r="Y79" s="8"/>
-      <c r="Z79" s="8"/>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>18</v>
       </c>
@@ -4730,15 +4694,8 @@
       <c r="R80" t="s">
         <v>18</v>
       </c>
-      <c r="T80" s="8"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="8"/>
-      <c r="W80" s="8"/>
-      <c r="X80" s="8"/>
-      <c r="Y80" s="8"/>
-      <c r="Z80" s="8"/>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>19</v>
       </c>
@@ -4793,15 +4750,8 @@
       <c r="R81" t="s">
         <v>18</v>
       </c>
-      <c r="T81" s="8"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="8"/>
-      <c r="W81" s="8"/>
-      <c r="X81" s="8"/>
-      <c r="Y81" s="8"/>
-      <c r="Z81" s="8"/>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>20</v>
       </c>
@@ -4856,15 +4806,8 @@
       <c r="R82" t="s">
         <v>18</v>
       </c>
-      <c r="T82" s="8"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="8"/>
-      <c r="W82" s="8"/>
-      <c r="X82" s="8"/>
-      <c r="Y82" s="8"/>
-      <c r="Z82" s="8"/>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>21</v>
       </c>
@@ -4919,15 +4862,8 @@
       <c r="R83" t="s">
         <v>18</v>
       </c>
-      <c r="T83" s="8"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="8"/>
-      <c r="W83" s="8"/>
-      <c r="X83" s="8"/>
-      <c r="Y83" s="8"/>
-      <c r="Z83" s="8"/>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>22</v>
       </c>
@@ -4982,15 +4918,8 @@
       <c r="R84" t="s">
         <v>18</v>
       </c>
-      <c r="T84" s="8"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="8"/>
-      <c r="W84" s="8"/>
-      <c r="X84" s="8"/>
-      <c r="Y84" s="8"/>
-      <c r="Z84" s="8"/>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>23</v>
       </c>
@@ -5045,15 +4974,8 @@
       <c r="R85" t="s">
         <v>18</v>
       </c>
-      <c r="T85" s="8"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="8"/>
-      <c r="W85" s="8"/>
-      <c r="X85" s="8"/>
-      <c r="Y85" s="8"/>
-      <c r="Z85" s="8"/>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>24</v>
       </c>
@@ -5109,7 +5031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>25</v>
       </c>
@@ -5165,7 +5087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>26</v>
       </c>
@@ -5221,7 +5143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>27</v>
       </c>
@@ -5277,7 +5199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>28</v>
       </c>
@@ -5333,7 +5255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>29</v>
       </c>
@@ -5389,7 +5311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="F92" s="2">
         <f>AVERAGE(F62:F91)</f>
         <v>1.5833333333333658E-3</v>
@@ -5415,12 +5337,12 @@
         <v>48.008130081300813</v>
       </c>
     </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
         <v>1</v>
       </c>
@@ -5473,7 +5395,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>0</v>
       </c>
@@ -5529,7 +5451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>1</v>
       </c>
@@ -6042,7 +5964,7 @@
         <f>AVERAGE(G95:G104)</f>
         <v>3.0000000000000027E-3</v>
       </c>
-      <c r="H105" s="9">
+      <c r="H105" s="8">
         <f>AVERAGE(H95:H104)</f>
         <v>1067</v>
       </c>
